--- a/artfynd/A 27322-2024 artfynd.xlsx
+++ b/artfynd/A 27322-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104022953</v>
+        <v>110969450</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tjäreberget-bäckedalen, Jmt</t>
+          <t>Tjäreberget, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>548114.0965781932</v>
+        <v>548051</v>
       </c>
       <c r="R2" t="n">
-        <v>7015641.647711786</v>
+        <v>7015648</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-07-19</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>14:37</t>
+          <t>2023-07-18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-07-19</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>14:37</t>
+          <t>2023-07-18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,53 +760,48 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+          <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>110969448</v>
+        <v>110969447</v>
       </c>
       <c r="B3" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>548049.0696618125</v>
+        <v>547964</v>
       </c>
       <c r="R3" t="n">
-        <v>7015647.88160193</v>
+        <v>7015651</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,19 +844,9 @@
           <t>2023-07-18</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-07-18</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,12 +880,7 @@
         <v>110969446</v>
       </c>
       <c r="B4" t="n">
-        <v>78579</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -947,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>548013.1712532972</v>
+        <v>548013</v>
       </c>
       <c r="R4" t="n">
-        <v>7015636.08815383</v>
+        <v>7015636</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,19 +945,9 @@
           <t>2023-07-18</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-07-18</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,50 +978,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>110969449</v>
+        <v>104022953</v>
       </c>
       <c r="B5" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tjäreberget, Jmt</t>
+          <t>Tjäreberget-bäckedalen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>548055.0110699898</v>
+        <v>548114</v>
       </c>
       <c r="R5" t="n">
-        <v>7015642.566500809</v>
+        <v>7015641</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,22 +1043,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2022-07-19</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2022-07-19</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,53 +1073,48 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Via Johan Staaf</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>SCA Skog Naturvärdesinventering</t>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>110969450</v>
+        <v>110969444</v>
       </c>
       <c r="B6" t="n">
-        <v>94134</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1179,10 +1124,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>548050.8729748757</v>
+        <v>548029</v>
       </c>
       <c r="R6" t="n">
-        <v>7015647.908516048</v>
+        <v>7015614</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,19 +1157,9 @@
           <t>2023-07-18</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-07-18</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,15 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>110969447</v>
+        <v>110969449</v>
       </c>
       <c r="B7" t="n">
-        <v>81248</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1271,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1295,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>547963.8027408754</v>
+        <v>548055</v>
       </c>
       <c r="R7" t="n">
-        <v>7015650.662988449</v>
+        <v>7015643</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1328,19 +1258,9 @@
           <t>2023-07-18</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-07-18</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1364,6 +1284,107 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>110969448</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Tjäreberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>548049</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7015648</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
         </is>

--- a/artfynd/A 27322-2024 artfynd.xlsx
+++ b/artfynd/A 27322-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110969450</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110969447</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110969446</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1086,6 +1106,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104022953</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1187,6 +1212,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110969444</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1288,6 +1318,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110969449</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1389,8 +1424,22 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110969448</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>